--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-medium_kitti.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-medium_kitti.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>25.11604046821594</v>
+        <v>20.52757143974304</v>
       </c>
       <c r="D2" t="n">
-        <v>1.340000033378601</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0548876283260491</v>
+        <v>0.0540716659277677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6079380512237549</v>
+        <v>0.5477786660194397</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6079380512237549</v>
+        <v>0.5477786660194397</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6070346236228943</v>
+        <v>0.5460923910140991</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6080940961837769</v>
+        <v>0.5451024770736694</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0428953282535076</v>
+        <v>0.045354176312685</v>
       </c>
       <c r="K2" t="n">
-        <v>67.19698047637939</v>
+        <v>61.53222179412842</v>
       </c>
       <c r="L2" t="n">
-        <v>1.318504095077515</v>
+        <v>1.370401620864868</v>
       </c>
       <c r="M2" t="n">
-        <v>12.01781511306763</v>
+        <v>11.81884145736694</v>
       </c>
       <c r="N2" t="n">
-        <v>75.18357753753662</v>
+        <v>11.51805448532104</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0263700819015502</v>
+        <v>0.0274080324172973</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2403563022613525</v>
+        <v>0.2363768291473388</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.503671550750732</v>
+        <v>0.2303610897064208</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-122540</t>
+          <t>20250720-051143</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -665,22 +665,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -690,10 +690,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -715,53 +715,53 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>20.11314606666565</v>
+        <v>20.40130543708801</v>
       </c>
       <c r="D3" t="n">
-        <v>1.470000028610229</v>
+        <v>1.309999942779541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0547685276716947</v>
+        <v>0.0543452378362416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5731629133224487</v>
+        <v>0.5525427460670471</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5731629133224487</v>
+        <v>0.5525427460670471</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5721580982208252</v>
+        <v>0.5508198738098145</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5705892443656921</v>
+        <v>0.5494404435157776</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0410336963832378</v>
+        <v>0.0462139807641506</v>
       </c>
       <c r="K3" t="n">
-        <v>61.7835054397583</v>
+        <v>61.31185054779053</v>
       </c>
       <c r="L3" t="n">
-        <v>1.360208034515381</v>
+        <v>1.425414562225342</v>
       </c>
       <c r="M3" t="n">
-        <v>11.64177846908569</v>
+        <v>11.56274580955505</v>
       </c>
       <c r="N3" t="n">
-        <v>45.76582598686218</v>
+        <v>11.65774154663086</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0272041606903076</v>
+        <v>0.0285082912445068</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2328355693817138</v>
+        <v>0.231254916191101</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9153165197372436</v>
+        <v>0.2331548309326171</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-122935</t>
+          <t>20250720-051426</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -811,10 +811,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -836,53 +836,53 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>20.14336252212524</v>
+        <v>20.3994083404541</v>
       </c>
       <c r="D4" t="n">
-        <v>1.289999961853027</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0545134250074624</v>
+        <v>0.0544982865452765</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5840655565261841</v>
+        <v>0.5651540756225586</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5840655565261841</v>
+        <v>0.5651540756225586</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5829944610595703</v>
+        <v>0.5639036297798157</v>
       </c>
       <c r="I4" t="n">
-        <v>0.583924412727356</v>
+        <v>0.5638020634651184</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0450482256710529</v>
+        <v>0.0487975105643272</v>
       </c>
       <c r="K4" t="n">
-        <v>60.70376539230347</v>
+        <v>61.45271396636963</v>
       </c>
       <c r="L4" t="n">
-        <v>1.399134635925293</v>
+        <v>1.439491510391235</v>
       </c>
       <c r="M4" t="n">
-        <v>11.57970547676086</v>
+        <v>11.68313527107239</v>
       </c>
       <c r="N4" t="n">
-        <v>11.89238691329956</v>
+        <v>11.46895432472229</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0279826927185058</v>
+        <v>0.0287898302078247</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2315941095352172</v>
+        <v>0.2336627054214477</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2378477382659912</v>
+        <v>0.2293790864944458</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-123251</t>
+          <t>20250720-051708</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -907,22 +907,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -932,10 +932,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -957,53 +957,53 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>20.12910795211792</v>
+        <v>20.35377836227417</v>
       </c>
       <c r="D5" t="n">
-        <v>1.289999961853027</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0549299042671918</v>
+        <v>0.0541083000600337</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6031777262687683</v>
+        <v>0.5894758701324463</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6031777262687683</v>
+        <v>0.5894758701324463</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6011986136436462</v>
+        <v>0.5878437757492065</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6023299098014832</v>
+        <v>0.5919977426528931</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0452051050961017</v>
+        <v>0.0459040254354476</v>
       </c>
       <c r="K5" t="n">
-        <v>59.72735500335693</v>
+        <v>60.98734426498413</v>
       </c>
       <c r="L5" t="n">
-        <v>1.411421775817871</v>
+        <v>1.364435911178589</v>
       </c>
       <c r="M5" t="n">
-        <v>11.42879939079285</v>
+        <v>11.65606260299683</v>
       </c>
       <c r="N5" t="n">
-        <v>11.69343161582947</v>
+        <v>11.90789866447449</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0282284355163574</v>
+        <v>0.0272887182235717</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2285759878158569</v>
+        <v>0.2331212520599365</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2338686323165893</v>
+        <v>0.2381579732894897</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-123532</t>
+          <t>20250720-051950</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1053,10 +1053,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>19.75437378883361</v>
+        <v>41.51702213287354</v>
       </c>
       <c r="D6" t="n">
-        <v>1.259999990463257</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0545427672564983</v>
+        <v>0.05456223660572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5987714529037476</v>
+        <v>0.6240959167480469</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5987714529037476</v>
+        <v>0.6240959167480469</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5969430208206177</v>
+        <v>0.622037410736084</v>
       </c>
       <c r="I6" t="n">
-        <v>0.60120689868927</v>
+        <v>0.6274129748344421</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0436598695814609</v>
+        <v>0.0430122464895248</v>
       </c>
       <c r="K6" t="n">
-        <v>60.03264713287354</v>
+        <v>60.93612456321716</v>
       </c>
       <c r="L6" t="n">
-        <v>1.356683492660522</v>
+        <v>1.428807497024536</v>
       </c>
       <c r="M6" t="n">
-        <v>11.68800687789917</v>
+        <v>11.82237982749939</v>
       </c>
       <c r="N6" t="n">
-        <v>12.00100207328796</v>
+        <v>11.52630567550659</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0271336698532104</v>
+        <v>0.0285761499404907</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2337601375579834</v>
+        <v>0.2364475965499878</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2400200414657592</v>
+        <v>0.2305261135101318</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-123810</t>
+          <t>20250720-052212</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1174,10 +1174,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
-        <v>42.39287519454956</v>
+        <v>133.9462451934814</v>
       </c>
       <c r="D2" t="n">
-        <v>2.859999895095825</v>
+        <v>2.910000085830688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1590860113501548</v>
+        <v>0.160545924130608</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2853165566921234</v>
+        <v>0.4517665803432464</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2853165566921234</v>
+        <v>0.4517665803432464</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2857981920242309</v>
+        <v>0.4512014389038086</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2843618094921112</v>
+        <v>0.4490492641925812</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0585985742509365</v>
+        <v>0.0763165205717086</v>
       </c>
       <c r="K2" t="n">
-        <v>150.5273265838623</v>
+        <v>151.2263889312744</v>
       </c>
       <c r="L2" t="n">
-        <v>1.768538236618042</v>
+        <v>2.145857572555542</v>
       </c>
       <c r="M2" t="n">
-        <v>11.31748867034912</v>
+        <v>13.0937294960022</v>
       </c>
       <c r="N2" t="n">
-        <v>32.68358612060547</v>
+        <v>14.91943264007568</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0353707647323608</v>
+        <v>0.0429171514511108</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2263497734069824</v>
+        <v>0.2618745899200439</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6536717224121094</v>
+        <v>0.2983886528015136</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-124225</t>
+          <t>20250718-091325</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1436,22 +1436,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1461,10 +1461,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>42.0854880809784</v>
+        <v>111.9925107955933</v>
       </c>
       <c r="D3" t="n">
-        <v>2.859999895095825</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1562261298298835</v>
+        <v>0.1612550962184156</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2830558717250824</v>
+        <v>0.4130090177059173</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2830558717250824</v>
+        <v>0.4130090177059173</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2827739715576172</v>
+        <v>0.4116256237030029</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2807796895503998</v>
+        <v>0.4061372876167297</v>
       </c>
       <c r="J3" t="n">
-        <v>0.060810413211584</v>
+        <v>0.07071553915739059</v>
       </c>
       <c r="K3" t="n">
-        <v>150.5516300201416</v>
+        <v>156.8985683917999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.752446174621582</v>
+        <v>2.065268278121948</v>
       </c>
       <c r="M3" t="n">
-        <v>13.37963652610779</v>
+        <v>11.98755764961243</v>
       </c>
       <c r="N3" t="n">
-        <v>30.73298406600952</v>
+        <v>15.60466933250427</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0350489234924316</v>
+        <v>0.0413053655624389</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2675927305221557</v>
+        <v>0.2397511529922485</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6146596813201904</v>
+        <v>0.3120933866500854</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-124712</t>
+          <t>20250718-091951</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1582,10 +1582,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>41.5115385055542</v>
+        <v>112.1377034187317</v>
       </c>
       <c r="D4" t="n">
-        <v>2.910000085830688</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1517031714320182</v>
+        <v>0.1604251313422407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2927548587322235</v>
+        <v>0.4129384756088257</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2927548587322235</v>
+        <v>0.4129384756088257</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2930794358253479</v>
+        <v>0.4128563702106476</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2924087047576904</v>
+        <v>0.4101705849170685</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06519944220781319</v>
+        <v>0.06551845371723169</v>
       </c>
       <c r="K4" t="n">
-        <v>151.1312665939331</v>
+        <v>156.706038236618</v>
       </c>
       <c r="L4" t="n">
-        <v>2.04491138458252</v>
+        <v>2.049185514450073</v>
       </c>
       <c r="M4" t="n">
-        <v>11.71651864051819</v>
+        <v>11.99470329284668</v>
       </c>
       <c r="N4" t="n">
-        <v>23.67155623435974</v>
+        <v>15.90052771568298</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0408982276916503</v>
+        <v>0.0409837102890014</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2343303728103637</v>
+        <v>0.2398940658569336</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4734311246871948</v>
+        <v>0.3180105543136596</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-125200</t>
+          <t>20250718-092600</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1678,22 +1678,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1703,10 +1703,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>41.74773073196411</v>
+        <v>111.7752413749695</v>
       </c>
       <c r="D5" t="n">
         <v>2.910000085830688</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1539249494671821</v>
+        <v>0.1610886257674012</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2978960871696472</v>
+        <v>0.4230669140815735</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2978960871696472</v>
+        <v>0.4230669140815735</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2981057167053222</v>
+        <v>0.4226053059101105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2968053817749023</v>
+        <v>0.4145322144031524</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06502595543861379</v>
+        <v>0.066204160451889</v>
       </c>
       <c r="K5" t="n">
-        <v>151.4420394897461</v>
+        <v>156.9411604404449</v>
       </c>
       <c r="L5" t="n">
-        <v>1.726373434066772</v>
+        <v>2.15453314781189</v>
       </c>
       <c r="M5" t="n">
-        <v>11.72292566299438</v>
+        <v>12.24849367141724</v>
       </c>
       <c r="N5" t="n">
-        <v>25.70911955833435</v>
+        <v>15.08715200424194</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0345274686813354</v>
+        <v>0.0430906629562377</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2344585132598877</v>
+        <v>0.2449698734283447</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.514182391166687</v>
+        <v>0.3017430400848389</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-125638</t>
+          <t>20250718-093149</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1799,22 +1799,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1824,10 +1824,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>42.1950421333313</v>
+        <v>100.6775925159454</v>
       </c>
       <c r="D6" t="n">
-        <v>2.859999895095825</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1565099537372589</v>
+        <v>0.1615421885251998</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2914266288280487</v>
+        <v>0.4120489656925201</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2914266288280487</v>
+        <v>0.4120489656925201</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2919739484786987</v>
+        <v>0.4103951156139374</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2911023199558258</v>
+        <v>0.4060394465923309</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06453981250524519</v>
+        <v>0.0669988468289375</v>
       </c>
       <c r="K6" t="n">
-        <v>150.626266002655</v>
+        <v>150.9486312866211</v>
       </c>
       <c r="L6" t="n">
-        <v>1.73141622543335</v>
+        <v>1.742536306381226</v>
       </c>
       <c r="M6" t="n">
-        <v>11.50901007652283</v>
+        <v>12.06932187080383</v>
       </c>
       <c r="N6" t="n">
-        <v>14.64656829833984</v>
+        <v>14.18993830680847</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0346283245086669</v>
+        <v>0.0348507261276245</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2301802015304565</v>
+        <v>0.2413864374160766</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2929313659667968</v>
+        <v>0.2837987661361694</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-130141</t>
+          <t>20250718-093758</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1945,10 +1945,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
-        <v>35.71473836898804</v>
+        <v>115.4617540836334</v>
       </c>
       <c r="D2" t="n">
-        <v>1.399999976158142</v>
+        <v>1.610000014305115</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1281300589442252</v>
+        <v>0.1351527961737968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2661957740783691</v>
+        <v>0.4237481951713562</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2661957740783691</v>
+        <v>0.4237481951713562</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2664611041545868</v>
+        <v>0.4231322109699249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2372349202632904</v>
+        <v>0.3877021074295044</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0584669224917888</v>
+        <v>0.0603897385299205</v>
       </c>
       <c r="K2" t="n">
-        <v>125.0313229560852</v>
+        <v>130.0059916973114</v>
       </c>
       <c r="L2" t="n">
-        <v>1.513335943222046</v>
+        <v>1.639606952667236</v>
       </c>
       <c r="M2" t="n">
-        <v>19.19762206077576</v>
+        <v>20.03147387504578</v>
       </c>
       <c r="N2" t="n">
-        <v>33.35957932472229</v>
+        <v>23.66655778884888</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0302667188644409</v>
+        <v>0.0327921390533447</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3839524412155151</v>
+        <v>0.4006294775009155</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6671915864944458</v>
+        <v>0.4733311557769775</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-154652</t>
+          <t>20250718-152046</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2207,22 +2207,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2232,10 +2232,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
-        <v>35.84003233909607</v>
+        <v>115.4242813587189</v>
       </c>
       <c r="D3" t="n">
         <v>1.399999976158142</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1275433488190174</v>
+        <v>0.1356206961414393</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2829754650592804</v>
+        <v>0.3987669348716736</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2829754650592804</v>
+        <v>0.3987669348716736</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2832747101783752</v>
+        <v>0.3977158665657043</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2523283958435058</v>
+        <v>0.3563243150711059</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0606401935219764</v>
+        <v>0.0546811781823635</v>
       </c>
       <c r="K3" t="n">
-        <v>124.2980945110321</v>
+        <v>129.3820557594299</v>
       </c>
       <c r="L3" t="n">
-        <v>1.569444417953491</v>
+        <v>1.60852313041687</v>
       </c>
       <c r="M3" t="n">
-        <v>19.71906352043152</v>
+        <v>19.87210345268249</v>
       </c>
       <c r="N3" t="n">
-        <v>28.90797734260559</v>
+        <v>24.05139756202698</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0313888883590698</v>
+        <v>0.0321704626083374</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3943812704086303</v>
+        <v>0.3974420690536499</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5781595468521118</v>
+        <v>0.4810279512405395</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-155114</t>
+          <t>20250718-152626</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2353,10 +2353,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>35.43893027305603</v>
+        <v>106.183084487915</v>
       </c>
       <c r="D4" t="n">
-        <v>1.399999976158142</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1265325956046581</v>
+        <v>0.1356003217158778</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2787169814109802</v>
+        <v>0.4033889174461365</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2787169814109802</v>
+        <v>0.4033889174461365</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2792242765426636</v>
+        <v>0.4032459855079651</v>
       </c>
       <c r="I4" t="n">
-        <v>0.25164994597435</v>
+        <v>0.3622593581676483</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0605229958891868</v>
+        <v>0.0595705993473529</v>
       </c>
       <c r="K4" t="n">
-        <v>124.7878315448761</v>
+        <v>124.307948589325</v>
       </c>
       <c r="L4" t="n">
-        <v>1.547607183456421</v>
+        <v>1.515774726867676</v>
       </c>
       <c r="M4" t="n">
-        <v>19.55228233337402</v>
+        <v>20.24419569969177</v>
       </c>
       <c r="N4" t="n">
-        <v>28.39403319358826</v>
+        <v>23.22528505325317</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0309521436691284</v>
+        <v>0.0303154945373535</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3910456466674805</v>
+        <v>0.4048839139938354</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5678806638717652</v>
+        <v>0.4645057010650635</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-155532</t>
+          <t>20250718-153206</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2474,10 +2474,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>35.60469269752502</v>
+        <v>75.39511871337891</v>
       </c>
       <c r="D5" t="n">
         <v>1.549999952316284</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1247986443340778</v>
+        <v>0.1320476626807993</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2833913266658783</v>
+        <v>0.3638768196105957</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2833913266658783</v>
+        <v>0.3638768196105957</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2833445072174072</v>
+        <v>0.363517016172409</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2550365924835205</v>
+        <v>0.2708837687969208</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0525520220398902</v>
+        <v>0.0596873573958873</v>
       </c>
       <c r="K5" t="n">
-        <v>125.2075757980347</v>
+        <v>129.4654428958893</v>
       </c>
       <c r="L5" t="n">
-        <v>1.549838542938232</v>
+        <v>1.60129714012146</v>
       </c>
       <c r="M5" t="n">
-        <v>19.3291847705841</v>
+        <v>19.94180369377136</v>
       </c>
       <c r="N5" t="n">
-        <v>29.25539088249207</v>
+        <v>23.57718324661255</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0309967708587646</v>
+        <v>0.0320259428024292</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3865836954116821</v>
+        <v>0.3988360738754272</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5851078176498413</v>
+        <v>0.4715436649322509</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-155949</t>
+          <t>20250718-153751</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2570,22 +2570,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2595,10 +2595,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>36.11355543136597</v>
+        <v>115.2088572978973</v>
       </c>
       <c r="D6" t="n">
-        <v>1.549999952316284</v>
+        <v>1.440000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1301374062895774</v>
+        <v>0.1341143767623339</v>
       </c>
       <c r="F6" t="n">
-        <v>0.276538610458374</v>
+        <v>0.4060217440128326</v>
       </c>
       <c r="G6" t="n">
-        <v>0.276538610458374</v>
+        <v>0.4060217440128326</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2769273817539215</v>
+        <v>0.4058507680892944</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2720743417739868</v>
+        <v>0.3391753733158111</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0560731515288353</v>
+        <v>0.0580806247889995</v>
       </c>
       <c r="K6" t="n">
-        <v>124.7109777927399</v>
+        <v>131.0028600692749</v>
       </c>
       <c r="L6" t="n">
-        <v>1.589812517166138</v>
+        <v>1.61350154876709</v>
       </c>
       <c r="M6" t="n">
-        <v>19.70651745796204</v>
+        <v>19.92676758766174</v>
       </c>
       <c r="N6" t="n">
-        <v>29.53937864303589</v>
+        <v>23.26251196861267</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0317962503433227</v>
+        <v>0.0322700309753418</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3941303491592407</v>
+        <v>0.3985353517532348</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5907875728607178</v>
+        <v>0.4652502393722534</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-160428</t>
+          <t>20250718-154251</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2716,10 +2716,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>80.35438942909241</v>
+        <v>190.8582165241241</v>
       </c>
       <c r="D2" t="n">
-        <v>8.840000152587891</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3266147524118423</v>
+        <v>0.333600206375122</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2662579417228699</v>
+        <v>0.3911347985267639</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2662579417228699</v>
+        <v>0.3911347985267639</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2662141621112823</v>
+        <v>0.3913124203681946</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2264691740274429</v>
+        <v>0.2567383348941803</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09875524789094919</v>
+        <v>0.1056228727102279</v>
       </c>
       <c r="K2" t="n">
-        <v>947.7851212024688</v>
+        <v>973.8744378089904</v>
       </c>
       <c r="L2" t="n">
-        <v>2.952287673950196</v>
+        <v>2.96519136428833</v>
       </c>
       <c r="M2" t="n">
-        <v>18.92150020599365</v>
+        <v>17.05132174491882</v>
       </c>
       <c r="N2" t="n">
-        <v>25.47431492805481</v>
+        <v>24.36248850822449</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0590457534790039</v>
+        <v>0.0593038272857666</v>
       </c>
       <c r="P2" t="n">
-        <v>0.378430004119873</v>
+        <v>0.3410264348983765</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5094862985610962</v>
+        <v>0.4872497701644897</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-194218</t>
+          <t>20250718-220701</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2978,22 +2978,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3003,10 +3003,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>80.74995017051697</v>
+        <v>102.4408695697784</v>
       </c>
       <c r="D3" t="n">
         <v>8.850000381469727</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3287199318408966</v>
+        <v>0.3302837999967428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2758334577083587</v>
+        <v>0.2990016639232635</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2758334577083587</v>
+        <v>0.2990016639232635</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2761708498001098</v>
+        <v>0.2995412647724151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2196225374937057</v>
+        <v>0.2676759362220764</v>
       </c>
       <c r="J3" t="n">
-        <v>0.109855443239212</v>
+        <v>0.1020927876234054</v>
       </c>
       <c r="K3" t="n">
-        <v>941.6560168266296</v>
+        <v>976.6500296592712</v>
       </c>
       <c r="L3" t="n">
-        <v>2.874335765838623</v>
+        <v>2.923272132873535</v>
       </c>
       <c r="M3" t="n">
-        <v>16.76624059677124</v>
+        <v>16.78148198127747</v>
       </c>
       <c r="N3" t="n">
-        <v>25.95124650001526</v>
+        <v>24.26127743721008</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0574867153167724</v>
+        <v>0.0584654426574707</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3353248119354248</v>
+        <v>0.3356296396255493</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5190249300003051</v>
+        <v>0.4852255487442016</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-200131</t>
+          <t>20250718-222829</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3124,10 +3124,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>80.31175851821899</v>
+        <v>211.8196465969086</v>
       </c>
       <c r="D4" t="n">
-        <v>8.840000152587891</v>
+        <v>8.939999580383301</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3271026849746704</v>
+        <v>0.3324132210441998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2913642227649688</v>
+        <v>0.4067957401275635</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2913642227649688</v>
+        <v>0.4067957401275635</v>
       </c>
       <c r="H4" t="n">
-        <v>0.291651964187622</v>
+        <v>0.4062599241733551</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2230660766363144</v>
+        <v>0.2983477413654327</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0998695343732833</v>
+        <v>0.0990283787250518</v>
       </c>
       <c r="K4" t="n">
-        <v>942.2900891304016</v>
+        <v>977.7318007946014</v>
       </c>
       <c r="L4" t="n">
-        <v>2.888306617736816</v>
+        <v>2.630060195922852</v>
       </c>
       <c r="M4" t="n">
-        <v>16.30146360397339</v>
+        <v>17.10669016838074</v>
       </c>
       <c r="N4" t="n">
-        <v>26.04159593582153</v>
+        <v>24.04936337471008</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0577661323547363</v>
+        <v>0.052601203918457</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3260292720794677</v>
+        <v>0.3421338033676147</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5208319187164306</v>
+        <v>0.4809872674942017</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-202036</t>
+          <t>20250718-224831</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3220,22 +3220,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -3245,10 +3245,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>80.69418716430664</v>
+        <v>210.816680431366</v>
       </c>
       <c r="D5" t="n">
-        <v>8.840000152587891</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3278979569673538</v>
+        <v>0.3299313890082495</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2951682507991791</v>
+        <v>0.4097784757614136</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2951682507991791</v>
+        <v>0.4097784757614136</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2952610552310943</v>
+        <v>0.4090437293052673</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2454745322465896</v>
+        <v>0.2749734222888946</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1006628721952438</v>
+        <v>0.0997120589017868</v>
       </c>
       <c r="K5" t="n">
-        <v>948.466774702072</v>
+        <v>978.6472358703612</v>
       </c>
       <c r="L5" t="n">
-        <v>2.865730047225952</v>
+        <v>2.637805461883545</v>
       </c>
       <c r="M5" t="n">
-        <v>16.75814437866211</v>
+        <v>17.73033666610718</v>
       </c>
       <c r="N5" t="n">
-        <v>25.30142426490784</v>
+        <v>24.37857151031494</v>
       </c>
       <c r="O5" t="n">
-        <v>0.057314600944519</v>
+        <v>0.0527561092376709</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3351628875732422</v>
+        <v>0.3546067333221435</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5060284852981567</v>
+        <v>0.4875714302062988</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-203939</t>
+          <t>20250718-231028</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3341,22 +3341,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -3366,10 +3366,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3391,53 +3391,53 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>80.43506813049316</v>
+        <v>81.18255043029785</v>
       </c>
       <c r="D6" t="n">
-        <v>8.840000152587891</v>
+        <v>8.850000381469727</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3265840262174606</v>
+        <v>0.3300811886787415</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2882652878761291</v>
+        <v>0.2792128622531891</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2882652878761291</v>
+        <v>0.2792128622531891</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2885810136795044</v>
+        <v>0.2787419855594635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2352756112813949</v>
+        <v>0.1763372123241424</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1017845645546913</v>
+        <v>0.1076367199420929</v>
       </c>
       <c r="K6" t="n">
-        <v>938.9185981750488</v>
+        <v>978.0680375099182</v>
       </c>
       <c r="L6" t="n">
-        <v>2.845995903015137</v>
+        <v>2.902377843856812</v>
       </c>
       <c r="M6" t="n">
-        <v>16.80641937255859</v>
+        <v>16.98725533485413</v>
       </c>
       <c r="N6" t="n">
-        <v>25.27481245994568</v>
+        <v>24.35928344726562</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0569199180603027</v>
+        <v>0.0580475568771362</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3361283874511718</v>
+        <v>0.3397451066970825</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5054962491989136</v>
+        <v>0.4871856689453125</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-205854</t>
+          <t>20250718-233221</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3462,22 +3462,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3487,10 +3487,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
-        <v>56.15666770935059</v>
+        <v>175.1578030586243</v>
       </c>
       <c r="D2" t="n">
         <v>7.840000152587891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2069604262709617</v>
+        <v>0.2056586865116567</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2648417353630066</v>
+        <v>0.4683456420898437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2648417353630066</v>
+        <v>0.4683456420898437</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2647110521793365</v>
+        <v>0.4672846496105194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2653563916683197</v>
+        <v>0.3660366833209991</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0843674167990684</v>
+        <v>0.0814096182584762</v>
       </c>
       <c r="K2" t="n">
-        <v>103.3231613636017</v>
+        <v>91.22695469856262</v>
       </c>
       <c r="L2" t="n">
-        <v>2.278682947158813</v>
+        <v>2.240718364715576</v>
       </c>
       <c r="M2" t="n">
-        <v>14.98099756240845</v>
+        <v>12.6483325958252</v>
       </c>
       <c r="N2" t="n">
-        <v>38.81025838851929</v>
+        <v>14.91847085952759</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0455736589431762</v>
+        <v>0.0448143672943115</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2996199512481689</v>
+        <v>0.2529666519165039</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7762051677703857</v>
+        <v>0.2983694171905517</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-053028</t>
+          <t>20250719-140114</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3749,22 +3749,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3774,10 +3774,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>56.10479784011841</v>
+        <v>130.7710728645325</v>
       </c>
       <c r="D3" t="n">
         <v>7.630000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.205662028491497</v>
+        <v>0.205525689125061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2701902389526367</v>
+        <v>0.4236522912979126</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2701902389526367</v>
+        <v>0.4236522912979126</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2699774801731109</v>
+        <v>0.4236462414264679</v>
       </c>
       <c r="I3" t="n">
-        <v>0.266914963722229</v>
+        <v>0.3541794419288635</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0845729187130928</v>
+        <v>0.080591008067131</v>
       </c>
       <c r="K3" t="n">
-        <v>91.33054995536804</v>
+        <v>92.14918756484984</v>
       </c>
       <c r="L3" t="n">
-        <v>2.260555267333984</v>
+        <v>2.564053535461426</v>
       </c>
       <c r="M3" t="n">
-        <v>13.17224335670471</v>
+        <v>14.02606439590454</v>
       </c>
       <c r="N3" t="n">
-        <v>16.21788454055786</v>
+        <v>15.09876918792725</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0452111053466796</v>
+        <v>0.0512810707092285</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2634448671340942</v>
+        <v>0.2805212879180908</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3243576908111572</v>
+        <v>0.3019753837585449</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-053511</t>
+          <t>20250719-140717</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3870,22 +3870,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3895,10 +3895,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>56.01032996177673</v>
+        <v>70.74515914916992</v>
       </c>
       <c r="D4" t="n">
         <v>7.630000114440918</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2068670138716697</v>
+        <v>0.2055993733497766</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2697254717350006</v>
+        <v>0.2850114703178406</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2697254717350006</v>
+        <v>0.2850114703178406</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2691570818424225</v>
+        <v>0.2844804227352142</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2534599900245666</v>
+        <v>0.2758349478244781</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0828011035919189</v>
+        <v>0.0826170369982719</v>
       </c>
       <c r="K4" t="n">
-        <v>90.50608205795288</v>
+        <v>90.90051126480104</v>
       </c>
       <c r="L4" t="n">
-        <v>2.180901765823364</v>
+        <v>2.510491371154785</v>
       </c>
       <c r="M4" t="n">
-        <v>12.97271680831909</v>
+        <v>13.73034310340881</v>
       </c>
       <c r="N4" t="n">
-        <v>15.96891975402832</v>
+        <v>14.98804259300232</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0436180353164672</v>
+        <v>0.0502098274230957</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2594543361663818</v>
+        <v>0.2746068620681762</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3193783950805664</v>
+        <v>0.2997608518600463</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-053915</t>
+          <t>20250719-141239</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3991,22 +3991,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4016,10 +4016,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>55.88118815422058</v>
+        <v>145.1372761726379</v>
       </c>
       <c r="D5" t="n">
         <v>7.630000114440918</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2071566388010978</v>
+        <v>0.2048501319118907</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2652213275432586</v>
+        <v>0.4401916265487671</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2652213275432586</v>
+        <v>0.4401916265487671</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2651308476924896</v>
+        <v>0.4395137131214142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2621243298053741</v>
+        <v>0.3906412124633789</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0899405255913734</v>
+        <v>0.0807969570159912</v>
       </c>
       <c r="K5" t="n">
-        <v>89.92948055267334</v>
+        <v>85.49673295021057</v>
       </c>
       <c r="L5" t="n">
-        <v>2.215404748916626</v>
+        <v>2.271787881851196</v>
       </c>
       <c r="M5" t="n">
-        <v>12.3692193031311</v>
+        <v>12.71565270423889</v>
       </c>
       <c r="N5" t="n">
-        <v>16.08204817771912</v>
+        <v>14.56949329376221</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0443080949783325</v>
+        <v>0.0454357576370239</v>
       </c>
       <c r="P5" t="n">
-        <v>0.247384386062622</v>
+        <v>0.2543130540847778</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3216409635543823</v>
+        <v>0.2913898658752441</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-054318</t>
+          <t>20250719-141658</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4112,22 +4112,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4137,10 +4137,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>56.09809708595276</v>
+        <v>174.6204152107239</v>
       </c>
       <c r="D6" t="n">
         <v>7.630000114440918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2055083513259887</v>
+        <v>0.2048239856958389</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2644022405147552</v>
+        <v>0.4786911010742187</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2644022405147552</v>
+        <v>0.4786911010742187</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2642350494861603</v>
+        <v>0.4782651960849762</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2614920735359192</v>
+        <v>0.405909925699234</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08343452215194699</v>
+        <v>0.08156531304121011</v>
       </c>
       <c r="K6" t="n">
-        <v>88.78582501411438</v>
+        <v>91.90048241615295</v>
       </c>
       <c r="L6" t="n">
-        <v>2.246242761611938</v>
+        <v>2.258429765701294</v>
       </c>
       <c r="M6" t="n">
-        <v>12.70378994941711</v>
+        <v>13.51828384399414</v>
       </c>
       <c r="N6" t="n">
-        <v>25.64028429985046</v>
+        <v>15.13105654716492</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0449248552322387</v>
+        <v>0.0451685953140258</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2540757989883422</v>
+        <v>0.2703656768798828</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5128056859970093</v>
+        <v>0.3026211309432983</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-054720</t>
+          <t>20250719-142231</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4233,22 +4233,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4258,10 +4258,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>36.17761301994324</v>
+        <v>74.35992121696472</v>
       </c>
       <c r="D2" t="n">
         <v>4.550000190734863</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1234359703958034</v>
+        <v>0.1236493915996767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2606536746025085</v>
+        <v>0.3002699017524719</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2606536746025085</v>
+        <v>0.3002699017524719</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2603411376476288</v>
+        <v>0.2999842762947082</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2591904401779175</v>
+        <v>0.2982749342918396</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0579888634383678</v>
+        <v>0.0628550723195076</v>
       </c>
       <c r="K2" t="n">
-        <v>54.3080427646637</v>
+        <v>54.85942673683167</v>
       </c>
       <c r="L2" t="n">
-        <v>1.582529544830322</v>
+        <v>1.575913429260254</v>
       </c>
       <c r="M2" t="n">
-        <v>12.34898281097412</v>
+        <v>11.67774248123169</v>
       </c>
       <c r="N2" t="n">
-        <v>72.92014527320862</v>
+        <v>11.73634505271912</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0316505908966064</v>
+        <v>0.031518268585205</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2469796562194824</v>
+        <v>0.2335548496246338</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.458402905464173</v>
+        <v>0.2347269010543823</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-082143</t>
+          <t>20250719-201537</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4545,10 +4545,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>36.08475613594055</v>
+        <v>179.7390105724335</v>
       </c>
       <c r="D3" t="n">
-        <v>4.550000190734863</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1227176398038863</v>
+        <v>0.1238180944865399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2585367858409881</v>
+        <v>0.4951680302619934</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2585367858409881</v>
+        <v>0.4951680302619934</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2585129737854004</v>
+        <v>0.4951901137828827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2575088143348694</v>
+        <v>0.4913871884346008</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0558104515075683</v>
+        <v>0.0579590313136577</v>
       </c>
       <c r="K3" t="n">
-        <v>54.09867143630981</v>
+        <v>56.26199555397034</v>
       </c>
       <c r="L3" t="n">
-        <v>1.920886278152466</v>
+        <v>1.534493446350098</v>
       </c>
       <c r="M3" t="n">
-        <v>11.33299779891968</v>
+        <v>11.3633508682251</v>
       </c>
       <c r="N3" t="n">
-        <v>22.22999453544617</v>
+        <v>11.78849458694458</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0384177255630493</v>
+        <v>0.0306898689270019</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2266599559783935</v>
+        <v>0.2272670173645019</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4445998907089233</v>
+        <v>0.2357698917388916</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-082543</t>
+          <t>20250719-201910</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4666,10 +4666,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n">
-        <v>36.36091566085816</v>
+        <v>160.2537596225739</v>
       </c>
       <c r="D4" t="n">
-        <v>4.590000152587891</v>
+        <v>4.800000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1235246993601321</v>
+        <v>0.1237723324067738</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2598245143890381</v>
+        <v>0.4846621751785278</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2598245143890381</v>
+        <v>0.4846621751785278</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2595915496349334</v>
+        <v>0.4838241934776306</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2600967586040497</v>
+        <v>0.483445405960083</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0557844825088977</v>
+        <v>0.059102039784193</v>
       </c>
       <c r="K4" t="n">
-        <v>50.73634815216064</v>
+        <v>56.40694332122803</v>
       </c>
       <c r="L4" t="n">
-        <v>1.582569360733032</v>
+        <v>1.570186853408814</v>
       </c>
       <c r="M4" t="n">
-        <v>10.82511067390442</v>
+        <v>10.80105805397034</v>
       </c>
       <c r="N4" t="n">
-        <v>17.60265421867371</v>
+        <v>12.52782201766968</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0316513872146606</v>
+        <v>0.0314037370681762</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2165022134780883</v>
+        <v>0.2160211610794067</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3520530843734741</v>
+        <v>0.2505564403533935</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-082831</t>
+          <t>20250719-202429</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4762,22 +4762,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4787,10 +4787,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>36.19358658790589</v>
+        <v>103.2883543968201</v>
       </c>
       <c r="D5" t="n">
-        <v>4.599999904632568</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1237199716269969</v>
+        <v>0.124272605824855</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2573687136173248</v>
+        <v>0.3336029648780823</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2573687136173248</v>
+        <v>0.3336029648780823</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2575339376926422</v>
+        <v>0.3328909277915954</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2574267387390136</v>
+        <v>0.329545646905899</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0589044094085693</v>
+        <v>0.0597343258559703</v>
       </c>
       <c r="K5" t="n">
-        <v>49.65849733352661</v>
+        <v>56.15585732460022</v>
       </c>
       <c r="L5" t="n">
-        <v>1.847701787948608</v>
+        <v>1.61366081237793</v>
       </c>
       <c r="M5" t="n">
-        <v>10.73759245872498</v>
+        <v>10.93164420127869</v>
       </c>
       <c r="N5" t="n">
-        <v>13.78063821792602</v>
+        <v>11.8900671005249</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0369540357589721</v>
+        <v>0.0322732162475585</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2147518491744995</v>
+        <v>0.2186328840255737</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2756127643585205</v>
+        <v>0.237801342010498</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-083131</t>
+          <t>20250719-202909</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4908,10 +4908,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>36.31331944465637</v>
+        <v>83.60356378555298</v>
       </c>
       <c r="D6" t="n">
-        <v>4.550000190734863</v>
+        <v>4.599999904632568</v>
       </c>
       <c r="E6" t="n">
-        <v>0.123351502418518</v>
+        <v>0.1239040237665176</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2579132318496704</v>
+        <v>0.2990590333938598</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2579132318496704</v>
+        <v>0.2990590333938598</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2581087052822113</v>
+        <v>0.2987432777881622</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2557693719863891</v>
+        <v>0.2961980998516083</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0551478117704391</v>
+        <v>0.0561449900269508</v>
       </c>
       <c r="K6" t="n">
-        <v>49.47989439964294</v>
+        <v>58.38636708259583</v>
       </c>
       <c r="L6" t="n">
-        <v>1.918653726577759</v>
+        <v>1.567954063415527</v>
       </c>
       <c r="M6" t="n">
-        <v>10.61607456207275</v>
+        <v>11.37536144256592</v>
       </c>
       <c r="N6" t="n">
-        <v>15.13701510429382</v>
+        <v>11.90068745613098</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0383730745315551</v>
+        <v>0.0313590812683105</v>
       </c>
       <c r="P6" t="n">
-        <v>0.212321491241455</v>
+        <v>0.2275072288513183</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3027403020858765</v>
+        <v>0.2380137491226196</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-083406</t>
+          <t>20250719-203311</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5029,10 +5029,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C2" t="n">
-        <v>31.95155119895935</v>
+        <v>193.8985047340393</v>
       </c>
       <c r="D2" t="n">
-        <v>3.390000104904175</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1097955495119094</v>
+        <v>0.1126428880353471</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2387714236974716</v>
+        <v>0.4185700714588165</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2387714236974716</v>
+        <v>0.4185700714588165</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2388695478439331</v>
+        <v>0.4179593920707702</v>
       </c>
       <c r="I2" t="n">
-        <v>0.237213522195816</v>
+        <v>0.4111811220645904</v>
       </c>
       <c r="J2" t="n">
-        <v>0.053315944969654</v>
+        <v>0.0551148205995559</v>
       </c>
       <c r="K2" t="n">
-        <v>46.42843389511109</v>
+        <v>46.28584265708923</v>
       </c>
       <c r="L2" t="n">
-        <v>1.363797903060913</v>
+        <v>1.371601581573486</v>
       </c>
       <c r="M2" t="n">
-        <v>10.87824273109436</v>
+        <v>11.07854413986206</v>
       </c>
       <c r="N2" t="n">
-        <v>52.60903382301331</v>
+        <v>12.6270112991333</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0272759580612182</v>
+        <v>0.0274320316314697</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2175648546218872</v>
+        <v>0.2215708827972412</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.052180676460266</v>
+        <v>0.252540225982666</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-102938</t>
+          <t>20250720-003640</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5291,22 +5291,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5316,10 +5316,10 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C3" t="n">
-        <v>32.20002484321594</v>
+        <v>168.2210640907288</v>
       </c>
       <c r="D3" t="n">
-        <v>3.390000104904175</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1108595088124274</v>
+        <v>0.1122196884504679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2476718723773956</v>
+        <v>0.438878059387207</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2476718723773956</v>
+        <v>0.438878059387207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2477526217699051</v>
+        <v>0.4394692480564117</v>
       </c>
       <c r="I3" t="n">
-        <v>0.246010422706604</v>
+        <v>0.4047566652297973</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0501105897128582</v>
+        <v>0.0580625161528587</v>
       </c>
       <c r="K3" t="n">
-        <v>47.42685747146606</v>
+        <v>46.79704928398132</v>
       </c>
       <c r="L3" t="n">
-        <v>1.390225648880005</v>
+        <v>1.445395231246948</v>
       </c>
       <c r="M3" t="n">
-        <v>10.54777503013611</v>
+        <v>10.78607797622681</v>
       </c>
       <c r="N3" t="n">
-        <v>12.69027066230774</v>
+        <v>12.73110699653626</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0278045129776</v>
+        <v>0.0289079046249389</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2109555006027221</v>
+        <v>0.2157215595245361</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2538054132461548</v>
+        <v>0.2546221399307251</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-103259</t>
+          <t>20250720-004204</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5437,10 +5437,10 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>32.13958716392517</v>
+        <v>84.51012969017029</v>
       </c>
       <c r="D4" t="n">
-        <v>3.390000104904175</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1098945185542106</v>
+        <v>0.1141645666211843</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2493131756782531</v>
+        <v>0.2877740263938904</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2493131756782531</v>
+        <v>0.2877740263938904</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2490895092487335</v>
+        <v>0.2876898348331451</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2480254620313644</v>
+        <v>0.2872839570045471</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0497784316539764</v>
+        <v>0.0543960370123386</v>
       </c>
       <c r="K4" t="n">
-        <v>46.35407137870789</v>
+        <v>46.8633406162262</v>
       </c>
       <c r="L4" t="n">
-        <v>1.721621513366699</v>
+        <v>1.41331672668457</v>
       </c>
       <c r="M4" t="n">
-        <v>10.68612003326416</v>
+        <v>11.00503516197205</v>
       </c>
       <c r="N4" t="n">
-        <v>12.32176399230957</v>
+        <v>12.29549622535706</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0344324302673339</v>
+        <v>0.0282663345336914</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2137224006652832</v>
+        <v>0.2201007032394409</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2464352798461914</v>
+        <v>0.2459099245071411</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-103540</t>
+          <t>20250720-004643</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5533,22 +5533,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5558,10 +5558,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="C5" t="n">
-        <v>32.2800440788269</v>
+        <v>192.6007981300354</v>
       </c>
       <c r="D5" t="n">
-        <v>3.390000104904175</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1114441670477389</v>
+        <v>0.1120775870200412</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2402778714895248</v>
+        <v>0.4431787431240082</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2402778714895248</v>
+        <v>0.4431787431240082</v>
       </c>
       <c r="H5" t="n">
-        <v>0.240090474486351</v>
+        <v>0.4429630935192108</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2348331362009048</v>
+        <v>0.4112288057804107</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0508023165166378</v>
+        <v>0.0544991493225097</v>
       </c>
       <c r="K5" t="n">
-        <v>46.70352339744568</v>
+        <v>46.80362677574158</v>
       </c>
       <c r="L5" t="n">
-        <v>1.41394567489624</v>
+        <v>1.408226490020752</v>
       </c>
       <c r="M5" t="n">
-        <v>10.60497641563416</v>
+        <v>10.94400548934936</v>
       </c>
       <c r="N5" t="n">
-        <v>12.10586524009705</v>
+        <v>12.20090246200562</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0282789134979248</v>
+        <v>0.028164529800415</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2120995283126831</v>
+        <v>0.2188801097869873</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2421173048019409</v>
+        <v>0.2440180492401123</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-103821</t>
+          <t>20250720-005018</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5679,10 +5679,10 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
-        <v>31.90504145622253</v>
+        <v>168.0719196796417</v>
       </c>
       <c r="D6" t="n">
-        <v>3.390000104904175</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1103077694773673</v>
+        <v>0.1120284010880979</v>
       </c>
       <c r="F6" t="n">
-        <v>0.248382419347763</v>
+        <v>0.4102377891540527</v>
       </c>
       <c r="G6" t="n">
-        <v>0.248382419347763</v>
+        <v>0.4102377891540527</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2485043406486511</v>
+        <v>0.4092753529548645</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2430148273706436</v>
+        <v>0.3994325697422027</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0507245175540447</v>
+        <v>0.0538615025579929</v>
       </c>
       <c r="K6" t="n">
-        <v>46.6704683303833</v>
+        <v>47.21846628189087</v>
       </c>
       <c r="L6" t="n">
-        <v>1.375340461730957</v>
+        <v>1.429876327514648</v>
       </c>
       <c r="M6" t="n">
-        <v>10.34063458442688</v>
+        <v>10.98369073867798</v>
       </c>
       <c r="N6" t="n">
-        <v>12.21123766899109</v>
+        <v>12.48749756813049</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0275068092346191</v>
+        <v>0.0285975265502929</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2068126916885376</v>
+        <v>0.2196738147735595</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2442247533798217</v>
+        <v>0.2497499513626098</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-104101</t>
+          <t>20250720-005542</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5775,22 +5775,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>9a4bab376</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5800,10 +5800,10 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-5ee82c27-cc18-d57b-22d9-5727a00ed3dc)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-078a6579-c608-a927-c277-fd8ba65603fb)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-dda4bc37-f438-79df-d6bb-6ee86a754b5a)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-c7ec0aa3-6571-2fc9-92d9-30a73ac97462)</t>
+          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-aa8a90a0-0bd8-2deb-5014-3b858b6bd164)
+GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-896f29ef-5953-5dff-c86d-99377a7a5780)
+GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-ce99d00a-0482-8a81-948f-d2cd4929e721)
+GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-ec7fc637-84c8-d1f9-4b8c-09625773cc3a)</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>workstation09</t>
+          <t>workstation06</t>
         </is>
       </c>
     </row>

--- a/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-medium_kitti.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/semantic_segmentation/SEMANTIC_SEGMENTATION-raw-medium_kitti.xlsx
@@ -591,56 +591,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>20.52757143974304</v>
+        <v>88.13932037353516</v>
       </c>
       <c r="D2" t="n">
-        <v>1.240000009536743</v>
+        <v>1.710000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0540716659277677</v>
+        <v>0.0546007539331912</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5477786660194397</v>
+        <v>0.6452046632766724</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5477786660194397</v>
+        <v>0.6452046632766724</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5460923910140991</v>
+        <v>0.6427842974662781</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5451024770736694</v>
+        <v>0.649542510509491</v>
       </c>
       <c r="J2" t="n">
-        <v>0.045354176312685</v>
+        <v>0.0453168600797653</v>
       </c>
       <c r="K2" t="n">
-        <v>61.53222179412842</v>
+        <v>62.15288281440735</v>
       </c>
       <c r="L2" t="n">
-        <v>1.370401620864868</v>
+        <v>1.388880014419556</v>
       </c>
       <c r="M2" t="n">
-        <v>11.81884145736694</v>
+        <v>11.96485757827759</v>
       </c>
       <c r="N2" t="n">
-        <v>11.51805448532104</v>
+        <v>11.62268209457398</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0274080324172973</v>
+        <v>0.0277776002883911</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2363768291473388</v>
+        <v>0.2392971515655517</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2303610897064208</v>
+        <v>0.2324536418914795</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-051143</t>
+          <t>20250723-155845</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -712,56 +712,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>20.40130543708801</v>
+        <v>73.49084377288818</v>
       </c>
       <c r="D3" t="n">
-        <v>1.309999942779541</v>
+        <v>1.860000014305115</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0543452378362416</v>
+        <v>0.0554709685284916</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5525427460670471</v>
+        <v>0.6462873220443726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5525427460670471</v>
+        <v>0.6462873220443726</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5508198738098145</v>
+        <v>0.6445876955986023</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5494404435157776</v>
+        <v>0.643964946269989</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0462139807641506</v>
+        <v>0.04713736474514</v>
       </c>
       <c r="K3" t="n">
-        <v>61.31185054779053</v>
+        <v>60.85340905189514</v>
       </c>
       <c r="L3" t="n">
-        <v>1.425414562225342</v>
+        <v>1.415415525436401</v>
       </c>
       <c r="M3" t="n">
-        <v>11.56274580955505</v>
+        <v>11.6487410068512</v>
       </c>
       <c r="N3" t="n">
-        <v>11.65774154663086</v>
+        <v>11.39374923706055</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0285082912445068</v>
+        <v>0.028308310508728</v>
       </c>
       <c r="P3" t="n">
-        <v>0.231254916191101</v>
+        <v>0.2329748201370239</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2331548309326171</v>
+        <v>0.2278749847412109</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-051426</t>
+          <t>20250723-160236</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -833,56 +833,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C4" t="n">
-        <v>20.3994083404541</v>
+        <v>112.919944524765</v>
       </c>
       <c r="D4" t="n">
-        <v>1.139999985694885</v>
+        <v>1.610000014305115</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0544982865452765</v>
+        <v>0.0545713326678825</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5651540756225586</v>
+        <v>0.6474820971488953</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5651540756225586</v>
+        <v>0.6474820971488953</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5639036297798157</v>
+        <v>0.6447937488555908</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5638020634651184</v>
+        <v>0.6470139026641846</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0487975105643272</v>
+        <v>0.0456940084695816</v>
       </c>
       <c r="K4" t="n">
-        <v>61.45271396636963</v>
+        <v>60.5561249256134</v>
       </c>
       <c r="L4" t="n">
-        <v>1.439491510391235</v>
+        <v>1.465419292449951</v>
       </c>
       <c r="M4" t="n">
-        <v>11.68313527107239</v>
+        <v>11.8465359210968</v>
       </c>
       <c r="N4" t="n">
-        <v>11.46895432472229</v>
+        <v>11.37203931808472</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0287898302078247</v>
+        <v>0.029308385848999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2336627054214477</v>
+        <v>0.236930718421936</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2293790864944458</v>
+        <v>0.2274407863616943</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-051708</t>
+          <t>20250723-160611</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -954,56 +954,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>20.35377836227417</v>
+        <v>93.6270673274994</v>
       </c>
       <c r="D5" t="n">
-        <v>1.360000014305115</v>
+        <v>1.539999961853027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0541083000600337</v>
+        <v>0.0551704175348551</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5894758701324463</v>
+        <v>0.6447796821594238</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5894758701324463</v>
+        <v>0.6447796821594238</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5878437757492065</v>
+        <v>0.6420283317565918</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5919977426528931</v>
+        <v>0.6457903385162354</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0459040254354476</v>
+        <v>0.0441273301839828</v>
       </c>
       <c r="K5" t="n">
-        <v>60.98734426498413</v>
+        <v>61.71850442886353</v>
       </c>
       <c r="L5" t="n">
-        <v>1.364435911178589</v>
+        <v>1.356578350067139</v>
       </c>
       <c r="M5" t="n">
-        <v>11.65606260299683</v>
+        <v>11.91469740867615</v>
       </c>
       <c r="N5" t="n">
-        <v>11.90789866447449</v>
+        <v>11.44478559494019</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0272887182235717</v>
+        <v>0.0271315670013427</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2331212520599365</v>
+        <v>0.2382939481735229</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2381579732894897</v>
+        <v>0.2288957118988037</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-051950</t>
+          <t>20250723-161025</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1075,56 +1075,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>41.51702213287354</v>
+        <v>83.76804876327515</v>
       </c>
       <c r="D6" t="n">
-        <v>1.509999990463257</v>
+        <v>1.659999966621399</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05456223660572</v>
+        <v>0.0547454317516468</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6240959167480469</v>
+        <v>0.6502156257629395</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6240959167480469</v>
+        <v>0.6502156257629395</v>
       </c>
       <c r="H6" t="n">
-        <v>0.622037410736084</v>
+        <v>0.6475490927696228</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6274129748344421</v>
+        <v>0.6470394134521484</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0430122464895248</v>
+        <v>0.0475033372640609</v>
       </c>
       <c r="K6" t="n">
-        <v>60.93612456321716</v>
+        <v>61.07670783996582</v>
       </c>
       <c r="L6" t="n">
-        <v>1.428807497024536</v>
+        <v>1.394713640213013</v>
       </c>
       <c r="M6" t="n">
-        <v>11.82237982749939</v>
+        <v>11.95404815673828</v>
       </c>
       <c r="N6" t="n">
-        <v>11.52630567550659</v>
+        <v>11.79253268241882</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0285761499404907</v>
+        <v>0.0278942728042602</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2364475965499878</v>
+        <v>0.2390809631347656</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2305261135101318</v>
+        <v>0.2358506536483764</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-052212</t>
+          <t>20250723-161422</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1362,56 +1362,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>133.9462451934814</v>
+        <v>195.7477293014526</v>
       </c>
       <c r="D2" t="n">
-        <v>2.910000085830688</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.160545924130608</v>
+        <v>0.1610426285862922</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4517665803432464</v>
+        <v>0.4697651863098144</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4517665803432464</v>
+        <v>0.4697651863098144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4512014389038086</v>
+        <v>0.4692513942718506</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4490492641925812</v>
+        <v>0.4571269452571869</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0763165205717086</v>
+        <v>0.07209683209657659</v>
       </c>
       <c r="K2" t="n">
-        <v>151.2263889312744</v>
+        <v>157.4015607833862</v>
       </c>
       <c r="L2" t="n">
-        <v>2.145857572555542</v>
+        <v>2.133305788040161</v>
       </c>
       <c r="M2" t="n">
-        <v>13.0937294960022</v>
+        <v>12.04214549064636</v>
       </c>
       <c r="N2" t="n">
-        <v>14.91943264007568</v>
+        <v>15.90970468521118</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0429171514511108</v>
+        <v>0.0426661157608032</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2618745899200439</v>
+        <v>0.2408429098129272</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2983886528015136</v>
+        <v>0.3181940937042236</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-091325</t>
+          <t>20250721-145939</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1483,56 +1483,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>111.9925107955933</v>
+        <v>218.7214205265045</v>
       </c>
       <c r="D3" t="n">
         <v>2.920000076293945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1612550962184156</v>
+        <v>0.1613119651696511</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4130090177059173</v>
+        <v>0.4485023617744446</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4130090177059173</v>
+        <v>0.4485023617744446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4116256237030029</v>
+        <v>0.4478132724761963</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4061372876167297</v>
+        <v>0.4355367422103882</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07071553915739059</v>
+        <v>0.06294120848178859</v>
       </c>
       <c r="K3" t="n">
-        <v>156.8985683917999</v>
+        <v>150.6599252223969</v>
       </c>
       <c r="L3" t="n">
-        <v>2.065268278121948</v>
+        <v>1.845977067947388</v>
       </c>
       <c r="M3" t="n">
-        <v>11.98755764961243</v>
+        <v>11.91755199432373</v>
       </c>
       <c r="N3" t="n">
-        <v>15.60466933250427</v>
+        <v>15.75876927375794</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0413053655624389</v>
+        <v>0.0369195413589477</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2397511529922485</v>
+        <v>0.2383510398864746</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3120933866500854</v>
+        <v>0.3151753854751586</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-091951</t>
+          <t>20250721-150652</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1604,56 +1604,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="C4" t="n">
-        <v>112.1377034187317</v>
+        <v>333.9670193195343</v>
       </c>
       <c r="D4" t="n">
         <v>2.920000076293945</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1604251313422407</v>
+        <v>0.1628709255262863</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4129384756088257</v>
+        <v>0.4584783911705017</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4129384756088257</v>
+        <v>0.4584783911705017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4128563702106476</v>
+        <v>0.4572561085224151</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4101705849170685</v>
+        <v>0.4499539136886596</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06551845371723169</v>
+        <v>0.0700366050004959</v>
       </c>
       <c r="K4" t="n">
-        <v>156.706038236618</v>
+        <v>150.6147050857544</v>
       </c>
       <c r="L4" t="n">
-        <v>2.049185514450073</v>
+        <v>1.799882888793945</v>
       </c>
       <c r="M4" t="n">
-        <v>11.99470329284668</v>
+        <v>11.81246852874756</v>
       </c>
       <c r="N4" t="n">
-        <v>15.90052771568298</v>
+        <v>15.84637546539307</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0409837102890014</v>
+        <v>0.0359976577758789</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2398940658569336</v>
+        <v>0.2362493705749511</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3180105543136596</v>
+        <v>0.3169275093078613</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-092600</t>
+          <t>20250721-151447</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1725,56 +1725,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>111.7752413749695</v>
+        <v>208.3998885154724</v>
       </c>
       <c r="D5" t="n">
         <v>2.910000085830688</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1610886257674012</v>
+        <v>0.1621986062459225</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4230669140815735</v>
+        <v>0.468248188495636</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4230669140815735</v>
+        <v>0.468248188495636</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4226053059101105</v>
+        <v>0.4683998525142669</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4145322144031524</v>
+        <v>0.4679312705993652</v>
       </c>
       <c r="J5" t="n">
-        <v>0.066204160451889</v>
+        <v>0.065649576485157</v>
       </c>
       <c r="K5" t="n">
-        <v>156.9411604404449</v>
+        <v>156.2185323238373</v>
       </c>
       <c r="L5" t="n">
-        <v>2.15453314781189</v>
+        <v>1.853682518005371</v>
       </c>
       <c r="M5" t="n">
-        <v>12.24849367141724</v>
+        <v>11.96514415740967</v>
       </c>
       <c r="N5" t="n">
-        <v>15.08715200424194</v>
+        <v>15.7358136177063</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0430906629562377</v>
+        <v>0.0370736503601074</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2449698734283447</v>
+        <v>0.2393028831481933</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3017430400848389</v>
+        <v>0.3147162723541259</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-093149</t>
+          <t>20250721-152418</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1846,56 +1846,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="C6" t="n">
-        <v>100.6775925159454</v>
+        <v>432.6247982978821</v>
       </c>
       <c r="D6" t="n">
-        <v>2.869999885559082</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1615421885251998</v>
+        <v>0.1611949078804623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4120489656925201</v>
+        <v>0.4710452556610107</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4120489656925201</v>
+        <v>0.4710452556610107</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4103951156139374</v>
+        <v>0.4702380001544952</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4060394465923309</v>
+        <v>0.4657208323478699</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0669988468289375</v>
+        <v>0.0665152743458747</v>
       </c>
       <c r="K6" t="n">
-        <v>150.9486312866211</v>
+        <v>151.8268890380859</v>
       </c>
       <c r="L6" t="n">
-        <v>1.742536306381226</v>
+        <v>1.850048065185547</v>
       </c>
       <c r="M6" t="n">
-        <v>12.06932187080383</v>
+        <v>11.72647619247436</v>
       </c>
       <c r="N6" t="n">
-        <v>14.18993830680847</v>
+        <v>14.44052505493164</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0348507261276245</v>
+        <v>0.0370009613037109</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2413864374160766</v>
+        <v>0.2345295238494873</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2837987661361694</v>
+        <v>0.2888105010986328</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-093758</t>
+          <t>20250721-153143</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2133,56 +2133,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
-        <v>115.4617540836334</v>
+        <v>252.224862575531</v>
       </c>
       <c r="D2" t="n">
-        <v>1.610000014305115</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1351527961737968</v>
+        <v>0.1331377554830018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4237481951713562</v>
+        <v>0.4536784887313843</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4237481951713562</v>
+        <v>0.4536784887313843</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4231322109699249</v>
+        <v>0.4527404606342315</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3877021074295044</v>
+        <v>0.4107494652271271</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0603897385299205</v>
+        <v>0.0585838034749031</v>
       </c>
       <c r="K2" t="n">
-        <v>130.0059916973114</v>
+        <v>130.6112024784088</v>
       </c>
       <c r="L2" t="n">
-        <v>1.639606952667236</v>
+        <v>1.58354640007019</v>
       </c>
       <c r="M2" t="n">
-        <v>20.03147387504578</v>
+        <v>19.71903824806213</v>
       </c>
       <c r="N2" t="n">
-        <v>23.66655778884888</v>
+        <v>23.56268715858459</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0327921390533447</v>
+        <v>0.0316709280014038</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4006294775009155</v>
+        <v>0.3943807649612427</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4733311557769775</v>
+        <v>0.4712537431716919</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-152046</t>
+          <t>20250721-214450</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2254,56 +2254,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C3" t="n">
-        <v>115.4242813587189</v>
+        <v>252.116678237915</v>
       </c>
       <c r="D3" t="n">
-        <v>1.399999976158142</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1356206961414393</v>
+        <v>0.1330619713702758</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3987669348716736</v>
+        <v>0.436394065618515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3987669348716736</v>
+        <v>0.436394065618515</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3977158665657043</v>
+        <v>0.435646116733551</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3563243150711059</v>
+        <v>0.387512743473053</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0546811781823635</v>
+        <v>0.0560638792812824</v>
       </c>
       <c r="K3" t="n">
-        <v>129.3820557594299</v>
+        <v>123.8614084720612</v>
       </c>
       <c r="L3" t="n">
-        <v>1.60852313041687</v>
+        <v>1.869972229003906</v>
       </c>
       <c r="M3" t="n">
-        <v>19.87210345268249</v>
+        <v>19.98712801933289</v>
       </c>
       <c r="N3" t="n">
-        <v>24.05139756202698</v>
+        <v>24.59734272956848</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0321704626083374</v>
+        <v>0.0373994445800781</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3974420690536499</v>
+        <v>0.3997425603866577</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4810279512405395</v>
+        <v>0.4919468545913696</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-152626</t>
+          <t>20250721-215247</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -2375,56 +2375,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C4" t="n">
-        <v>106.183084487915</v>
+        <v>223.671324968338</v>
       </c>
       <c r="D4" t="n">
-        <v>1.600000023841858</v>
+        <v>1.399999976158142</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1356003217158778</v>
+        <v>0.1333754964391975</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4033889174461365</v>
+        <v>0.4457840621471405</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4033889174461365</v>
+        <v>0.4457840621471405</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4032459855079651</v>
+        <v>0.4446690380573272</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3622593581676483</v>
+        <v>0.3640230298042297</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0595705993473529</v>
+        <v>0.0629190281033515</v>
       </c>
       <c r="K4" t="n">
-        <v>124.307948589325</v>
+        <v>124.2154800891876</v>
       </c>
       <c r="L4" t="n">
-        <v>1.515774726867676</v>
+        <v>1.606998920440674</v>
       </c>
       <c r="M4" t="n">
-        <v>20.24419569969177</v>
+        <v>20.25959038734436</v>
       </c>
       <c r="N4" t="n">
-        <v>23.22528505325317</v>
+        <v>23.51861071586609</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0303154945373535</v>
+        <v>0.0321399784088134</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4048839139938354</v>
+        <v>0.4051918077468872</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4645057010650635</v>
+        <v>0.4703722143173218</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-153206</t>
+          <t>20250721-220104</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2496,56 +2496,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="C5" t="n">
-        <v>75.39511871337891</v>
+        <v>329.4982750415802</v>
       </c>
       <c r="D5" t="n">
-        <v>1.549999952316284</v>
+        <v>1.659999966621399</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1320476626807993</v>
+        <v>0.133508220610052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3638768196105957</v>
+        <v>0.4639649093151092</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3638768196105957</v>
+        <v>0.4639649093151092</v>
       </c>
       <c r="H5" t="n">
-        <v>0.363517016172409</v>
+        <v>0.4629997313022613</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2708837687969208</v>
+        <v>0.4211870431900024</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0596873573958873</v>
+        <v>0.0575284399092197</v>
       </c>
       <c r="K5" t="n">
-        <v>129.4654428958893</v>
+        <v>130.9398944377899</v>
       </c>
       <c r="L5" t="n">
-        <v>1.60129714012146</v>
+        <v>1.639220476150513</v>
       </c>
       <c r="M5" t="n">
-        <v>19.94180369377136</v>
+        <v>20.11902666091919</v>
       </c>
       <c r="N5" t="n">
-        <v>23.57718324661255</v>
+        <v>24.74307632446289</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0320259428024292</v>
+        <v>0.0327844095230102</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3988360738754272</v>
+        <v>0.4023805332183838</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4715436649322509</v>
+        <v>0.4948615264892578</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-153751</t>
+          <t>20250721-220847</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2617,56 +2617,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2088572978973</v>
+        <v>233.3326570987701</v>
       </c>
       <c r="D6" t="n">
-        <v>1.440000057220459</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1341143767623339</v>
+        <v>0.132992310633122</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4060217440128326</v>
+        <v>0.4490236341953277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4060217440128326</v>
+        <v>0.4490236341953277</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4058507680892944</v>
+        <v>0.4485222101211548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3391753733158111</v>
+        <v>0.3713410794734955</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0580806247889995</v>
+        <v>0.0551003739237785</v>
       </c>
       <c r="K6" t="n">
-        <v>131.0028600692749</v>
+        <v>130.2090141773224</v>
       </c>
       <c r="L6" t="n">
-        <v>1.61350154876709</v>
+        <v>1.611768484115601</v>
       </c>
       <c r="M6" t="n">
-        <v>19.92676758766174</v>
+        <v>20.22424650192261</v>
       </c>
       <c r="N6" t="n">
-        <v>23.26251196861267</v>
+        <v>24.71484971046448</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0322700309753418</v>
+        <v>0.032235369682312</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3985353517532348</v>
+        <v>0.4044849300384521</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4652502393722534</v>
+        <v>0.4942969942092896</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-154251</t>
+          <t>20250721-221803</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2904,56 +2904,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n">
-        <v>190.8582165241241</v>
+        <v>713.7208557128906</v>
       </c>
       <c r="D2" t="n">
-        <v>9.039999961853027</v>
+        <v>8.939999580383301</v>
       </c>
       <c r="E2" t="n">
-        <v>0.333600206375122</v>
+        <v>0.3308266158006629</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3911347985267639</v>
+        <v>0.4886717200279236</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3911347985267639</v>
+        <v>0.4886717200279236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3913124203681946</v>
+        <v>0.4880945980548858</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2567383348941803</v>
+        <v>0.2449550628662109</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1056228727102279</v>
+        <v>0.1017046198248863</v>
       </c>
       <c r="K2" t="n">
-        <v>973.8744378089904</v>
+        <v>975.7566556930542</v>
       </c>
       <c r="L2" t="n">
-        <v>2.96519136428833</v>
+        <v>2.969379425048828</v>
       </c>
       <c r="M2" t="n">
-        <v>17.05132174491882</v>
+        <v>17.62345361709595</v>
       </c>
       <c r="N2" t="n">
-        <v>24.36248850822449</v>
+        <v>24.12212896347046</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0593038272857666</v>
+        <v>0.0593875885009765</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3410264348983765</v>
+        <v>0.3524690723419189</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4872497701644897</v>
+        <v>0.4824425792694092</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250718-220701</t>
+          <t>20250722-053446</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3025,56 +3025,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="C3" t="n">
-        <v>102.4408695697784</v>
+        <v>718.0211563110352</v>
       </c>
       <c r="D3" t="n">
-        <v>8.850000381469727</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3302837999967428</v>
+        <v>0.3326712874125461</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2990016639232635</v>
+        <v>0.4892435073852539</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2990016639232635</v>
+        <v>0.4892435073852539</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2995412647724151</v>
+        <v>0.4886777102947235</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2676759362220764</v>
+        <v>0.2238646894693374</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1020927876234054</v>
+        <v>0.1001090034842491</v>
       </c>
       <c r="K3" t="n">
-        <v>976.6500296592712</v>
+        <v>982.526517868042</v>
       </c>
       <c r="L3" t="n">
-        <v>2.923272132873535</v>
+        <v>3.00438928604126</v>
       </c>
       <c r="M3" t="n">
-        <v>16.78148198127747</v>
+        <v>17.11440849304199</v>
       </c>
       <c r="N3" t="n">
-        <v>24.26127743721008</v>
+        <v>24.36747717857361</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0584654426574707</v>
+        <v>0.0600877857208251</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3356296396255493</v>
+        <v>0.3422881698608398</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4852255487442016</v>
+        <v>0.4873495435714721</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250718-222829</t>
+          <t>20250722-060500</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3146,56 +3146,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
-        <v>211.8196465969086</v>
+        <v>649.8944928646088</v>
       </c>
       <c r="D4" t="n">
-        <v>8.939999580383301</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3324132210441998</v>
+        <v>0.3306527097573441</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4067957401275635</v>
+        <v>0.4841629564762115</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4067957401275635</v>
+        <v>0.4841629564762115</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4062599241733551</v>
+        <v>0.483445942401886</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2983477413654327</v>
+        <v>0.2810301482677459</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0990283787250518</v>
+        <v>0.1154869869351387</v>
       </c>
       <c r="K4" t="n">
-        <v>977.7318007946014</v>
+        <v>978.803914308548</v>
       </c>
       <c r="L4" t="n">
-        <v>2.630060195922852</v>
+        <v>3.038255929946899</v>
       </c>
       <c r="M4" t="n">
-        <v>17.10669016838074</v>
+        <v>17.52176094055176</v>
       </c>
       <c r="N4" t="n">
-        <v>24.04936337471008</v>
+        <v>24.19540548324585</v>
       </c>
       <c r="O4" t="n">
-        <v>0.052601203918457</v>
+        <v>0.0607651185989379</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3421338033676147</v>
+        <v>0.3504352188110352</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4809872674942017</v>
+        <v>0.483908109664917</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250718-224831</t>
+          <t>20250722-063523</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3267,56 +3267,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>210.816680431366</v>
+        <v>715.8210687637329</v>
       </c>
       <c r="D5" t="n">
         <v>8.890000343322754</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3299313890082495</v>
+        <v>0.331692100483544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4097784757614136</v>
+        <v>0.503938615322113</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4097784757614136</v>
+        <v>0.503938615322113</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4090437293052673</v>
+        <v>0.5025500059127808</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2749734222888946</v>
+        <v>0.183896318078041</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0997120589017868</v>
+        <v>0.1036709249019622</v>
       </c>
       <c r="K5" t="n">
-        <v>978.6472358703612</v>
+        <v>970.9590723514556</v>
       </c>
       <c r="L5" t="n">
-        <v>2.637805461883545</v>
+        <v>2.980468273162842</v>
       </c>
       <c r="M5" t="n">
-        <v>17.73033666610718</v>
+        <v>17.6532678604126</v>
       </c>
       <c r="N5" t="n">
-        <v>24.37857151031494</v>
+        <v>24.77122688293457</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0527561092376709</v>
+        <v>0.0596093654632568</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3546067333221435</v>
+        <v>0.3530653572082519</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4875714302062988</v>
+        <v>0.4954245376586914</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250718-231028</t>
+          <t>20250722-070435</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3388,56 +3388,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="C6" t="n">
-        <v>81.18255043029785</v>
+        <v>694.2382683753967</v>
       </c>
       <c r="D6" t="n">
-        <v>8.850000381469727</v>
+        <v>8.890000343322754</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3300811886787415</v>
+        <v>0.331962356755608</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2792128622531891</v>
+        <v>0.4994610548019409</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2792128622531891</v>
+        <v>0.4994610548019409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2787419855594635</v>
+        <v>0.4990462362766266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1763372123241424</v>
+        <v>0.1754195094108581</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1076367199420929</v>
+        <v>0.1065553277730941</v>
       </c>
       <c r="K6" t="n">
-        <v>978.0680375099182</v>
+        <v>976.181475162506</v>
       </c>
       <c r="L6" t="n">
-        <v>2.902377843856812</v>
+        <v>2.669222593307495</v>
       </c>
       <c r="M6" t="n">
-        <v>16.98725533485413</v>
+        <v>16.69099760055542</v>
       </c>
       <c r="N6" t="n">
-        <v>24.35928344726562</v>
+        <v>24.04360580444336</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0580475568771362</v>
+        <v>0.0533844518661499</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3397451066970825</v>
+        <v>0.3338199520111084</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4871856689453125</v>
+        <v>0.4808721160888672</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250718-233221</t>
+          <t>20250722-073445</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3675,56 +3675,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C2" t="n">
-        <v>175.1578030586243</v>
+        <v>354.5404434204102</v>
       </c>
       <c r="D2" t="n">
-        <v>7.840000152587891</v>
+        <v>7.630000114440918</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2056586865116567</v>
+        <v>0.2054640476552533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4683456420898437</v>
+        <v>0.5167165994644165</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4683456420898437</v>
+        <v>0.5167165994644165</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4672846496105194</v>
+        <v>0.5154715180397034</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3660366833209991</v>
+        <v>0.5052416920661926</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0814096182584762</v>
+        <v>0.0844548493623733</v>
       </c>
       <c r="K2" t="n">
-        <v>91.22695469856262</v>
+        <v>91.72026586532591</v>
       </c>
       <c r="L2" t="n">
-        <v>2.240718364715576</v>
+        <v>2.295273065567017</v>
       </c>
       <c r="M2" t="n">
-        <v>12.6483325958252</v>
+        <v>14.09366250038147</v>
       </c>
       <c r="N2" t="n">
-        <v>14.91847085952759</v>
+        <v>15.25928592681885</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0448143672943115</v>
+        <v>0.0459054613113403</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2529666519165039</v>
+        <v>0.2818732500076294</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2983694171905517</v>
+        <v>0.3051857185363769</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-140114</t>
+          <t>20250722-222447</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3796,56 +3796,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="C3" t="n">
-        <v>130.7710728645325</v>
+        <v>881.0989637374878</v>
       </c>
       <c r="D3" t="n">
-        <v>7.630000114440918</v>
+        <v>7.889999866485596</v>
       </c>
       <c r="E3" t="n">
-        <v>0.205525689125061</v>
+        <v>0.2051959309165038</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4236522912979126</v>
+        <v>0.6703747510910034</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4236522912979126</v>
+        <v>0.6703747510910034</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4236462414264679</v>
+        <v>0.6674538850784302</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3541794419288635</v>
+        <v>0.6577269434928894</v>
       </c>
       <c r="J3" t="n">
-        <v>0.080591008067131</v>
+        <v>0.0875391289591789</v>
       </c>
       <c r="K3" t="n">
-        <v>92.14918756484984</v>
+        <v>91.66342163085938</v>
       </c>
       <c r="L3" t="n">
-        <v>2.564053535461426</v>
+        <v>2.257901668548584</v>
       </c>
       <c r="M3" t="n">
-        <v>14.02606439590454</v>
+        <v>13.62667059898376</v>
       </c>
       <c r="N3" t="n">
-        <v>15.09876918792725</v>
+        <v>15.27976298332214</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0512810707092285</v>
+        <v>0.0451580333709716</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2805212879180908</v>
+        <v>0.2725334119796753</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3019753837585449</v>
+        <v>0.3055952596664428</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-140717</t>
+          <t>20250722-223352</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3917,56 +3917,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="C4" t="n">
-        <v>70.74515914916992</v>
+        <v>694.035640001297</v>
       </c>
       <c r="D4" t="n">
-        <v>7.630000114440918</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2055993733497766</v>
+        <v>0.2065994743789945</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2850114703178406</v>
+        <v>0.65211021900177</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2850114703178406</v>
+        <v>0.65211021900177</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2844804227352142</v>
+        <v>0.6491871476173401</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2758349478244781</v>
+        <v>0.6254994869232178</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0826170369982719</v>
+        <v>0.08105719834566109</v>
       </c>
       <c r="K4" t="n">
-        <v>90.90051126480104</v>
+        <v>91.8325560092926</v>
       </c>
       <c r="L4" t="n">
-        <v>2.510491371154785</v>
+        <v>2.560828685760498</v>
       </c>
       <c r="M4" t="n">
-        <v>13.73034310340881</v>
+        <v>14.17004299163818</v>
       </c>
       <c r="N4" t="n">
-        <v>14.98804259300232</v>
+        <v>14.92995619773865</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0502098274230957</v>
+        <v>0.0512165737152099</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2746068620681762</v>
+        <v>0.2834008598327637</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2997608518600463</v>
+        <v>0.2985991239547729</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-141239</t>
+          <t>20250722-225143</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4038,56 +4038,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="C5" t="n">
-        <v>145.1372761726379</v>
+        <v>894.1988983154297</v>
       </c>
       <c r="D5" t="n">
-        <v>7.630000114440918</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2048501319118907</v>
+        <v>0.2048228762962006</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4401916265487671</v>
+        <v>0.6532579064369202</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4401916265487671</v>
+        <v>0.6532579064369202</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4395137131214142</v>
+        <v>0.6510894298553467</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3906412124633789</v>
+        <v>0.6427297592163086</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0807969570159912</v>
+        <v>0.0824759751558303</v>
       </c>
       <c r="K5" t="n">
-        <v>85.49673295021057</v>
+        <v>85.21728110313416</v>
       </c>
       <c r="L5" t="n">
-        <v>2.271787881851196</v>
+        <v>2.290252447128296</v>
       </c>
       <c r="M5" t="n">
-        <v>12.71565270423889</v>
+        <v>13.4404513835907</v>
       </c>
       <c r="N5" t="n">
-        <v>14.56949329376221</v>
+        <v>15.43336200714111</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0454357576370239</v>
+        <v>0.0458050489425659</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2543130540847778</v>
+        <v>0.2688090276718139</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2913898658752441</v>
+        <v>0.3086672401428222</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-141658</t>
+          <t>20250722-230628</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4159,56 +4159,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>174.6204152107239</v>
+        <v>719.5053727626801</v>
       </c>
       <c r="D6" t="n">
-        <v>7.630000114440918</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2048239856958389</v>
+        <v>0.2049596852635684</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4786911010742187</v>
+        <v>0.6486351490020752</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4786911010742187</v>
+        <v>0.6486351490020752</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4782651960849762</v>
+        <v>0.6468481421470642</v>
       </c>
       <c r="I6" t="n">
-        <v>0.405909925699234</v>
+        <v>0.6391127109527588</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08156531304121011</v>
+        <v>0.08171588927507401</v>
       </c>
       <c r="K6" t="n">
-        <v>91.90048241615295</v>
+        <v>92.5019552707672</v>
       </c>
       <c r="L6" t="n">
-        <v>2.258429765701294</v>
+        <v>2.528982162475586</v>
       </c>
       <c r="M6" t="n">
-        <v>13.51828384399414</v>
+        <v>13.10109782218933</v>
       </c>
       <c r="N6" t="n">
-        <v>15.13105654716492</v>
+        <v>14.93619561195374</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0451685953140258</v>
+        <v>0.0505796432495117</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2703656768798828</v>
+        <v>0.2620219564437866</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3026211309432983</v>
+        <v>0.2987239122390747</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-142231</t>
+          <t>20250722-232406</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4446,56 +4446,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n">
-        <v>74.35992121696472</v>
+        <v>312.697990655899</v>
       </c>
       <c r="D2" t="n">
-        <v>4.550000190734863</v>
+        <v>4.75</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1236493915996767</v>
+        <v>0.1240392711241634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3002699017524719</v>
+        <v>0.5240787267684937</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3002699017524719</v>
+        <v>0.5240787267684937</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2999842762947082</v>
+        <v>0.5224137902259827</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2982749342918396</v>
+        <v>0.5220950245857239</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0628550723195076</v>
+        <v>0.0585867017507553</v>
       </c>
       <c r="K2" t="n">
-        <v>54.85942673683167</v>
+        <v>50.35202479362488</v>
       </c>
       <c r="L2" t="n">
-        <v>1.575913429260254</v>
+        <v>1.918392658233642</v>
       </c>
       <c r="M2" t="n">
-        <v>11.67774248123169</v>
+        <v>10.93724870681763</v>
       </c>
       <c r="N2" t="n">
-        <v>11.73634505271912</v>
+        <v>12.55615162849426</v>
       </c>
       <c r="O2" t="n">
-        <v>0.031518268585205</v>
+        <v>0.0383678531646728</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2335548496246338</v>
+        <v>0.2187449741363525</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2347269010543823</v>
+        <v>0.2511230325698853</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250719-201537</t>
+          <t>20250723-053752</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4567,56 +4567,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>122</v>
       </c>
       <c r="C3" t="n">
-        <v>179.7390105724335</v>
+        <v>388.4110999107361</v>
       </c>
       <c r="D3" t="n">
-        <v>4.599999904632568</v>
+        <v>4.75</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1238180944865399</v>
+        <v>0.1241840576661414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4951680302619934</v>
+        <v>0.527009904384613</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4951680302619934</v>
+        <v>0.527009904384613</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4951901137828827</v>
+        <v>0.5256802439689636</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4913871884346008</v>
+        <v>0.5111366510391235</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0579590313136577</v>
+        <v>0.0553893856704235</v>
       </c>
       <c r="K3" t="n">
-        <v>56.26199555397034</v>
+        <v>56.60994839668274</v>
       </c>
       <c r="L3" t="n">
-        <v>1.534493446350098</v>
+        <v>1.591190338134766</v>
       </c>
       <c r="M3" t="n">
-        <v>11.3633508682251</v>
+        <v>10.96271014213562</v>
       </c>
       <c r="N3" t="n">
-        <v>11.78849458694458</v>
+        <v>12.03156614303589</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0306898689270019</v>
+        <v>0.0318238067626953</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2272670173645019</v>
+        <v>0.2192542028427124</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2357698917388916</v>
+        <v>0.2406313228607177</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250719-201910</t>
+          <t>20250723-054524</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4688,56 +4688,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="C4" t="n">
-        <v>160.2537596225739</v>
+        <v>374.0815486907959</v>
       </c>
       <c r="D4" t="n">
         <v>4.800000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1237723324067738</v>
+        <v>0.12482294324657</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4846621751785278</v>
+        <v>0.5256470441818237</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4846621751785278</v>
+        <v>0.5256470441818237</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4838241934776306</v>
+        <v>0.5240249037742615</v>
       </c>
       <c r="I4" t="n">
-        <v>0.483445405960083</v>
+        <v>0.5171349048614502</v>
       </c>
       <c r="J4" t="n">
-        <v>0.059102039784193</v>
+        <v>0.0598012916743755</v>
       </c>
       <c r="K4" t="n">
-        <v>56.40694332122803</v>
+        <v>56.09726548194885</v>
       </c>
       <c r="L4" t="n">
-        <v>1.570186853408814</v>
+        <v>1.572998762130737</v>
       </c>
       <c r="M4" t="n">
-        <v>10.80105805397034</v>
+        <v>11.21794009208679</v>
       </c>
       <c r="N4" t="n">
-        <v>12.52782201766968</v>
+        <v>12.13442015647888</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0314037370681762</v>
+        <v>0.0314599752426147</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2160211610794067</v>
+        <v>0.2243588018417358</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2505564403533935</v>
+        <v>0.2426884031295776</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250719-202429</t>
+          <t>20250723-055412</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4809,56 +4809,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="C5" t="n">
-        <v>103.2883543968201</v>
+        <v>443.5911948680878</v>
       </c>
       <c r="D5" t="n">
-        <v>4.550000190734863</v>
+        <v>4.75</v>
       </c>
       <c r="E5" t="n">
-        <v>0.124272605824855</v>
+        <v>0.1242437560111283</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3336029648780823</v>
+        <v>0.5342601537704468</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3336029648780823</v>
+        <v>0.5342601537704468</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3328909277915954</v>
+        <v>0.5333905816078186</v>
       </c>
       <c r="I5" t="n">
-        <v>0.329545646905899</v>
+        <v>0.5309594869613647</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0597343258559703</v>
+        <v>0.059686966240406</v>
       </c>
       <c r="K5" t="n">
-        <v>56.15585732460022</v>
+        <v>49.95479345321655</v>
       </c>
       <c r="L5" t="n">
-        <v>1.61366081237793</v>
+        <v>1.582266807556152</v>
       </c>
       <c r="M5" t="n">
-        <v>10.93164420127869</v>
+        <v>10.93307518959045</v>
       </c>
       <c r="N5" t="n">
-        <v>11.8900671005249</v>
+        <v>12.49486112594604</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0322732162475585</v>
+        <v>0.031645336151123</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2186328840255737</v>
+        <v>0.218661503791809</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.237801342010498</v>
+        <v>0.2498972225189209</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250719-202909</t>
+          <t>20250723-060246</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4930,56 +4930,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="C6" t="n">
-        <v>83.60356378555298</v>
+        <v>380.8384349346161</v>
       </c>
       <c r="D6" t="n">
-        <v>4.599999904632568</v>
+        <v>4.800000190734863</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1239040237665176</v>
+        <v>0.1252358621534179</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2990590333938598</v>
+        <v>0.5214743614196777</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2990590333938598</v>
+        <v>0.5214743614196777</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2987432777881622</v>
+        <v>0.5208370685577393</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2961980998516083</v>
+        <v>0.5191090703010559</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0561449900269508</v>
+        <v>0.0614785961806774</v>
       </c>
       <c r="K6" t="n">
-        <v>58.38636708259583</v>
+        <v>55.74189281463623</v>
       </c>
       <c r="L6" t="n">
-        <v>1.567954063415527</v>
+        <v>1.587918281555176</v>
       </c>
       <c r="M6" t="n">
-        <v>11.37536144256592</v>
+        <v>11.15030002593994</v>
       </c>
       <c r="N6" t="n">
-        <v>11.90068745613098</v>
+        <v>11.77418065071106</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0313590812683105</v>
+        <v>0.0317583656311035</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2275072288513183</v>
+        <v>0.2230060005187988</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2380137491226196</v>
+        <v>0.2354836130142212</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250719-203311</t>
+          <t>20250723-061208</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5217,56 +5217,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="C2" t="n">
-        <v>193.8985047340393</v>
+        <v>429.4770653247833</v>
       </c>
       <c r="D2" t="n">
-        <v>3.490000009536743</v>
+        <v>3.549999952316284</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1126428880353471</v>
+        <v>0.1122261741149582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4185700714588165</v>
+        <v>0.5152665376663208</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4185700714588165</v>
+        <v>0.5152665376663208</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4179593920707702</v>
+        <v>0.514476478099823</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4111811220645904</v>
+        <v>0.5104241371154785</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0551148205995559</v>
+        <v>0.0543323904275894</v>
       </c>
       <c r="K2" t="n">
-        <v>46.28584265708923</v>
+        <v>41.23922848701477</v>
       </c>
       <c r="L2" t="n">
-        <v>1.371601581573486</v>
+        <v>1.385035276412964</v>
       </c>
       <c r="M2" t="n">
-        <v>11.07854413986206</v>
+        <v>10.77791452407837</v>
       </c>
       <c r="N2" t="n">
-        <v>12.6270112991333</v>
+        <v>11.88388609886169</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0274320316314697</v>
+        <v>0.0277007055282592</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2215708827972412</v>
+        <v>0.2155582904815673</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.252540225982666</v>
+        <v>0.2376777219772338</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250720-003640</t>
+          <t>20250723-110554</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5338,56 +5338,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C3" t="n">
-        <v>168.2210640907288</v>
+        <v>296.3008978366852</v>
       </c>
       <c r="D3" t="n">
-        <v>3.450000047683716</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1122196884504679</v>
+        <v>0.1125720025111849</v>
       </c>
       <c r="F3" t="n">
-        <v>0.438878059387207</v>
+        <v>0.4793019294738769</v>
       </c>
       <c r="G3" t="n">
-        <v>0.438878059387207</v>
+        <v>0.4793019294738769</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4394692480564117</v>
+        <v>0.4782452583312988</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4047566652297973</v>
+        <v>0.461651861667633</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0580625161528587</v>
+        <v>0.0506718531250953</v>
       </c>
       <c r="K3" t="n">
-        <v>46.79704928398132</v>
+        <v>46.66630601882935</v>
       </c>
       <c r="L3" t="n">
-        <v>1.445395231246948</v>
+        <v>1.372283697128296</v>
       </c>
       <c r="M3" t="n">
-        <v>10.78607797622681</v>
+        <v>10.76703429222107</v>
       </c>
       <c r="N3" t="n">
-        <v>12.73110699653626</v>
+        <v>12.25769376754761</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0289079046249389</v>
+        <v>0.0274456739425659</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2157215595245361</v>
+        <v>0.2153406858444214</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2546221399307251</v>
+        <v>0.2451538753509521</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250720-004204</t>
+          <t>20250723-111513</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5459,56 +5459,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="C4" t="n">
-        <v>84.51012969017029</v>
+        <v>396.6273419857025</v>
       </c>
       <c r="D4" t="n">
-        <v>3.450000047683716</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1141645666211843</v>
+        <v>0.1126973718404769</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2877740263938904</v>
+        <v>0.488871157169342</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2877740263938904</v>
+        <v>0.488871157169342</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2876898348331451</v>
+        <v>0.4884556829929352</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2872839570045471</v>
+        <v>0.4714649319648742</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0543960370123386</v>
+        <v>0.0580510906875133</v>
       </c>
       <c r="K4" t="n">
-        <v>46.8633406162262</v>
+        <v>46.42569065093994</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41331672668457</v>
+        <v>1.408702850341797</v>
       </c>
       <c r="M4" t="n">
-        <v>11.00503516197205</v>
+        <v>10.8785252571106</v>
       </c>
       <c r="N4" t="n">
-        <v>12.29549622535706</v>
+        <v>11.91532897949219</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0282663345336914</v>
+        <v>0.0281740570068359</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2201007032394409</v>
+        <v>0.2175705051422119</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2459099245071411</v>
+        <v>0.2383065795898437</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250720-004643</t>
+          <t>20250723-112220</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5580,56 +5580,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>192.6007981300354</v>
+        <v>354.0525698661804</v>
       </c>
       <c r="D5" t="n">
         <v>3.490000009536743</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1120775870200412</v>
+        <v>0.1126544579267501</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4431787431240082</v>
+        <v>0.4911050498485565</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4431787431240082</v>
+        <v>0.4911050498485565</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4429630935192108</v>
+        <v>0.4902929067611694</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4112288057804107</v>
+        <v>0.4807385206222534</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0544991493225097</v>
+        <v>0.0546525940299034</v>
       </c>
       <c r="K5" t="n">
-        <v>46.80362677574158</v>
+        <v>47.33771204948425</v>
       </c>
       <c r="L5" t="n">
-        <v>1.408226490020752</v>
+        <v>1.413070678710938</v>
       </c>
       <c r="M5" t="n">
-        <v>10.94400548934936</v>
+        <v>10.8770923614502</v>
       </c>
       <c r="N5" t="n">
-        <v>12.20090246200562</v>
+        <v>12.0596809387207</v>
       </c>
       <c r="O5" t="n">
-        <v>0.028164529800415</v>
+        <v>0.0282614135742187</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2188801097869873</v>
+        <v>0.2175418472290039</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2440180492401123</v>
+        <v>0.241193618774414</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250720-005018</t>
+          <t>20250723-113106</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5701,56 +5701,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="C6" t="n">
-        <v>168.0719196796417</v>
+        <v>289.2699604034424</v>
       </c>
       <c r="D6" t="n">
-        <v>3.440000057220459</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1120284010880979</v>
+        <v>0.1134191326575703</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4102377891540527</v>
+        <v>0.4986432194709778</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4102377891540527</v>
+        <v>0.4986432194709778</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4092753529548645</v>
+        <v>0.4979535043239593</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3994325697422027</v>
+        <v>0.4877395927906036</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0538615025579929</v>
+        <v>0.0542120561003685</v>
       </c>
       <c r="K6" t="n">
-        <v>47.21846628189087</v>
+        <v>46.54412508010864</v>
       </c>
       <c r="L6" t="n">
-        <v>1.429876327514648</v>
+        <v>1.391931295394898</v>
       </c>
       <c r="M6" t="n">
-        <v>10.98369073867798</v>
+        <v>10.61539912223816</v>
       </c>
       <c r="N6" t="n">
-        <v>12.48749756813049</v>
+        <v>12.80074048042297</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0285975265502929</v>
+        <v>0.0278386259078979</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2196738147735595</v>
+        <v>0.2123079824447631</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2497499513626098</v>
+        <v>0.2560148096084594</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250720-005542</t>
+          <t>20250723-113911</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
